--- a/www/BYD收款退款单上传模板.xlsx
+++ b/www/BYD收款退款单上传模板.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\棱星数据\Desktop\DF\DF\单据\销售\2026单据\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CSV_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062C11D0-C5A8-4139-A884-BD472E7AC614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD7A159-A1D5-4A83-BA3A-C5B621599DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
   <si>
     <t>过账日期</t>
   </si>
@@ -110,6 +110,28 @@
   </si>
   <si>
     <t>公司名称</t>
+  </si>
+  <si>
+    <t>公司货币余额</t>
+  </si>
+  <si>
+    <t>交易货币借方金额</t>
+  </si>
+  <si>
+    <t>交易货币贷方金额</t>
+  </si>
+  <si>
+    <t>交易货币余额</t>
+  </si>
+  <si>
+    <t>28,000.00 CNY</t>
+  </si>
+  <si>
+    <t>-28,000.00 CNY</t>
+  </si>
+  <si>
+    <t>TEST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -463,14 +485,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
     <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" customWidth="1"/>
+    <col min="11" max="11" width="4.88671875" customWidth="1"/>
+    <col min="14" max="14" width="7.77734375" customWidth="1"/>
+    <col min="16" max="16" width="16.44140625" customWidth="1"/>
+    <col min="17" max="17" width="12.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
@@ -522,10 +549,23 @@
       <c r="Q1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="R1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="V1" s="2"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>11210200</v>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>36</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -572,10 +612,21 @@
       <c r="P2" t="s">
         <v>20</v>
       </c>
+      <c r="R2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="V2" s="2"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>11210200</v>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>36</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -622,6 +673,17 @@
       <c r="P3" t="s">
         <v>23</v>
       </c>
+      <c r="R3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V3" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
